--- a/Packages/cn.etetet.twsmap/Luban/Config/Datas/EnergyBlock.xlsx
+++ b/Packages/cn.etetet.twsmap/Luban/Config/Datas/EnergyBlock.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>速度_1</t>
+  </si>
+  <si>
+    <t>对局持续时间_0</t>
   </si>
   <si>
     <t>能量块_m</t>
@@ -1046,7 +1049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" customWidth="1"/>
@@ -1135,55 +1138,81 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="3">
+    <row r="6" s="2" customFormat="1" spans="2:5">
+      <c r="B6" s="3"/>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2">
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="3"/>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="3"/>
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E9" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2">
-        <v>50</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
+      <c r="E10" s="2">
+        <v>100</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="3"/>
-      <c r="D7" s="2" t="s">
+    <row r="11" spans="4:5">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E11" s="2">
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="3">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2">
-        <v>100</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="4:5">
-      <c r="D9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5000</v>
+    <row r="12" spans="4:5">
+      <c r="D12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30000</v>
       </c>
     </row>
   </sheetData>
